--- a/apps_Maurice_MAK_REINFORCE/dose_response_3species_5rxns/dose_response_3species_5rxns_MAK_REINFORCE.xlsx
+++ b/apps_Maurice_MAK_REINFORCE/dose_response_3species_5rxns/dose_response_3species_5rxns_MAK_REINFORCE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,16 @@
           <t>2025-11-12 15:42:44</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2025-11-20 12:35:48</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2025-11-20 12:51:57</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -589,6 +599,16 @@
           <t>https://www.comet.com/redsnic/dose-response-3species-5rxns-mak-reinforce/42fe92e1453649669fab2f2d39f31b3d</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/dose-response-3species-5rxns-mak-reinforce/64a9153667fe471281a1d9386803a356</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/dose-response-3species-5rxns-mak-reinforce/e8ead9ac460a4e65ba2520a497035a38</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -644,6 +664,12 @@
       <c r="Q3" t="n">
         <v>5</v>
       </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -699,6 +725,12 @@
       <c r="Q4" t="n">
         <v>3</v>
       </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -754,6 +786,12 @@
       <c r="Q5" t="n">
         <v>1</v>
       </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,6 +847,12 @@
       <c r="Q6" t="n">
         <v>240</v>
       </c>
+      <c r="R6" t="n">
+        <v>3840</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3840</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -864,6 +908,12 @@
       <c r="Q7" t="b">
         <v>0</v>
       </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -919,6 +969,12 @@
       <c r="Q8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="R8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -974,6 +1030,12 @@
       <c r="Q9" t="n">
         <v>300</v>
       </c>
+      <c r="R9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1029,6 +1091,12 @@
       <c r="Q10" t="n">
         <v>5</v>
       </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1084,6 +1152,12 @@
       <c r="Q11" t="n">
         <v>1024</v>
       </c>
+      <c r="R11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1139,6 +1213,12 @@
       <c r="Q12" t="n">
         <v>10240</v>
       </c>
+      <c r="R12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1194,6 +1274,12 @@
       <c r="Q13" t="n">
         <v>8</v>
       </c>
+      <c r="R13" t="n">
+        <v>128</v>
+      </c>
+      <c r="S13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1281,6 +1367,16 @@
           <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1368,6 +1464,16 @@
           <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1423,6 +1529,12 @@
       <c r="Q16" t="n">
         <v>1</v>
       </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1478,6 +1590,12 @@
       <c r="Q17" t="n">
         <v>10</v>
       </c>
+      <c r="R17" t="n">
+        <v>10</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1533,6 +1651,12 @@
       <c r="Q18" t="n">
         <v>100</v>
       </c>
+      <c r="R18" t="n">
+        <v>100</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1588,6 +1712,12 @@
       <c r="Q19" t="n">
         <v>1000</v>
       </c>
+      <c r="R19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1643,6 +1773,12 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1698,6 +1834,12 @@
       <c r="Q21" t="n">
         <v>20</v>
       </c>
+      <c r="R21" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1781,6 +1923,16 @@
         </is>
       </c>
       <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>{'type': 'lognormal_1D'}</t>
         </is>
